--- a/matuik.xlsx
+++ b/matuik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\GitHub\web-tufe-flask\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB5B97E-6955-45A2-8012-4526D482F070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32CEBB13-F404-460B-B660-B8149F56D0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Gösterge</t>
   </si>
@@ -139,6 +139,9 @@
   </si>
   <si>
     <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
   </si>
 </sst>
 </file>
@@ -566,13 +569,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -612,172 +615,187 @@
       <c r="M1" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="10">
-        <v>2.0531449398624999</v>
+        <v>2.0531446489813998</v>
       </c>
       <c r="C2" s="10">
-        <v>2.3982370040404</v>
+        <v>2.3982370405269999</v>
       </c>
       <c r="D2" s="10">
-        <v>2.5228834268576001</v>
+        <v>2.5228835203197</v>
       </c>
       <c r="E2" s="10">
-        <v>1.9613860004376</v>
+        <v>1.9613864787158</v>
       </c>
       <c r="F2" s="10">
-        <v>2.0059693981293001</v>
+        <v>2.0059697751943002</v>
       </c>
       <c r="G2" s="10">
-        <v>2.6464439285558998</v>
+        <v>2.6464439290589001</v>
       </c>
       <c r="H2" s="10">
-        <v>2.4263475648349</v>
+        <v>2.4263472959943999</v>
       </c>
       <c r="I2" s="10">
-        <v>2.6610992222859</v>
+        <v>2.6610988596687002</v>
       </c>
       <c r="J2" s="10">
-        <v>2.0424982486590002</v>
+        <v>2.0424981318025002</v>
       </c>
       <c r="K2" s="10">
-        <v>1.4837657488314</v>
+        <v>1.4837661912904001</v>
       </c>
       <c r="L2" s="10">
-        <v>1.6540951602269001</v>
+        <v>1.6540950569996</v>
       </c>
       <c r="M2" s="10">
-        <v>2.8775612001176998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.7007589135069998</v>
+      </c>
+      <c r="N2" s="10">
+        <v>2.7555452488253001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="10">
-        <v>2.411876871094</v>
+        <v>2.4118766111030001</v>
       </c>
       <c r="C3" s="10">
-        <v>1.7421582420420001</v>
+        <v>1.7421585735039999</v>
       </c>
       <c r="D3" s="10">
-        <v>2.6986848122649998</v>
+        <v>2.6986849158930002</v>
       </c>
       <c r="E3" s="10">
-        <v>2.0474493317340001</v>
+        <v>2.0474495447079999</v>
       </c>
       <c r="F3" s="10">
-        <v>1.9996663618949999</v>
+        <v>1.9996665283849999</v>
       </c>
       <c r="G3" s="10">
-        <v>2.2176600603900001</v>
+        <v>2.2176599730579998</v>
       </c>
       <c r="H3" s="10">
-        <v>2.1530939315830002</v>
+        <v>2.1530935381949998</v>
       </c>
       <c r="I3" s="10">
-        <v>2.5443750375779999</v>
+        <v>2.5443750951370001</v>
       </c>
       <c r="J3" s="10">
-        <v>2.0177371611789998</v>
+        <v>2.01773707131</v>
       </c>
       <c r="K3" s="10">
-        <v>1.9655951234319999</v>
+        <v>1.965595449531</v>
       </c>
       <c r="L3" s="10">
-        <v>1.9418925005900001</v>
+        <v>1.9418924773949999</v>
       </c>
       <c r="M3" s="10">
-        <v>2.4960977226400001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.2718539342190001</v>
+      </c>
+      <c r="N3" s="10">
+        <v>2.3983357684739999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
       <c r="B4" s="10">
-        <v>1.907571234832</v>
+        <v>1.9075709870999999</v>
       </c>
       <c r="C4" s="10">
-        <v>2.0085324267429998</v>
+        <v>2.0085328925580002</v>
       </c>
       <c r="D4" s="10">
-        <v>2.84630112422</v>
+        <v>2.846301172105</v>
       </c>
       <c r="E4" s="10">
-        <v>2.1924838183330002</v>
+        <v>2.1924841171959999</v>
       </c>
       <c r="F4" s="10">
-        <v>2.2265661315590002</v>
+        <v>2.2265663287169999</v>
       </c>
       <c r="G4" s="10">
-        <v>2.226225892804</v>
+        <v>2.2262257421820002</v>
       </c>
       <c r="H4" s="10">
-        <v>1.7881061150169999</v>
+        <v>1.7881057731009999</v>
       </c>
       <c r="I4" s="10">
-        <v>2.24438416399</v>
+        <v>2.2443841084309999</v>
       </c>
       <c r="J4" s="10">
-        <v>1.9072118976900001</v>
+        <v>1.907211849726</v>
       </c>
       <c r="K4" s="10">
-        <v>2.0707382264269998</v>
+        <v>2.0707385901130002</v>
       </c>
       <c r="L4" s="10">
-        <v>2.0482711955120001</v>
+        <v>2.0482710825120001</v>
       </c>
       <c r="M4" s="10">
-        <v>2.453925746685</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.1816625192360002</v>
+      </c>
+      <c r="N4" s="10">
+        <v>1.803304574717</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
       <c r="B5" s="10">
-        <v>1.608018473285</v>
+        <v>1.6080181815386001</v>
       </c>
       <c r="C5" s="10">
-        <v>2.2700170525569998</v>
+        <v>2.2700168775290002</v>
       </c>
       <c r="D5" s="10">
-        <v>2.3500944439909999</v>
+        <v>2.3500943233807998</v>
       </c>
       <c r="E5" s="10">
-        <v>1.691171159022</v>
+        <v>1.6911716527306999</v>
       </c>
       <c r="F5" s="10">
-        <v>1.5185746819970001</v>
+        <v>1.5185751453187</v>
       </c>
       <c r="G5" s="10">
-        <v>2.3796498045050001</v>
+        <v>2.3796498156596</v>
       </c>
       <c r="H5" s="10">
-        <v>2.3203764897250001</v>
+        <v>2.3203763774969999</v>
       </c>
       <c r="I5" s="10">
-        <v>2.6091221814779999</v>
+        <v>2.6091217333726</v>
       </c>
       <c r="J5" s="10">
-        <v>1.6546450197710001</v>
+        <v>1.6546449468836</v>
       </c>
       <c r="K5" s="10">
-        <v>0.80609129699399995</v>
+        <v>0.80609182257269996</v>
       </c>
       <c r="L5" s="10">
-        <v>1.03065463162</v>
+        <v>1.0306544233735</v>
       </c>
       <c r="M5" s="10">
-        <v>3.0069925394000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.912741734785</v>
+      </c>
+      <c r="N5" s="10">
+        <v>2.7947756388478</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -817,213 +835,231 @@
       <c r="M6" s="10">
         <v>2.29257354324402</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6" s="10">
+        <v>1.97189374482363</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="10">
-        <v>2.0018468403954</v>
+        <v>2.0018459368721002</v>
       </c>
       <c r="C7" s="10">
-        <v>3.3789485256434002</v>
+        <v>3.3789477439582001</v>
       </c>
       <c r="D7" s="10">
-        <v>1.2669273203372</v>
+        <v>1.2669273657174001</v>
       </c>
       <c r="E7" s="10">
-        <v>1.5658711898072</v>
+        <v>1.5658723375831001</v>
       </c>
       <c r="F7" s="10">
-        <v>1.560494431965</v>
+        <v>1.5604957005952</v>
       </c>
       <c r="G7" s="10">
-        <v>1.2303030922527001</v>
+        <v>1.2303035166808001</v>
       </c>
       <c r="H7" s="10">
-        <v>4.4032057094821004</v>
+        <v>4.4032053748160003</v>
       </c>
       <c r="I7" s="10">
-        <v>4.6751387892486003</v>
+        <v>4.6751374805010002</v>
       </c>
       <c r="J7" s="10">
-        <v>2.5814192275166001</v>
+        <v>2.5814188173454</v>
       </c>
       <c r="K7" s="10">
-        <v>-0.2428315694963</v>
+        <v>-0.24283076085870001</v>
       </c>
       <c r="L7" s="10">
-        <v>1.5831218669702001</v>
+        <v>1.5831216963599</v>
       </c>
       <c r="M7" s="10">
-        <v>4.1283765133347998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>4.1324448020829001</v>
+      </c>
+      <c r="N7" s="10">
+        <v>5.3429283566796997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="10">
-        <v>-1.2961596287237001</v>
+        <v>-1.29616123818511</v>
       </c>
       <c r="C8" s="10">
-        <v>7.0291861985736803</v>
+        <v>7.0291847921686399</v>
       </c>
       <c r="D8" s="10">
-        <v>0.32533547922229</v>
+        <v>0.32533511880513</v>
       </c>
       <c r="E8" s="10">
-        <v>1.7793992375316801</v>
+        <v>1.77940202806086</v>
       </c>
       <c r="F8" s="10">
-        <v>2.29172447579904</v>
+        <v>2.2917272818118199</v>
       </c>
       <c r="G8" s="10">
-        <v>7.3507498077899996E-2</v>
+        <v>7.3508214745619999E-2</v>
       </c>
       <c r="H8" s="10">
-        <v>5.1143877480503299</v>
+        <v>5.1143877721476798</v>
       </c>
       <c r="I8" s="10">
-        <v>5.6322687006104202</v>
+        <v>5.63226505427994</v>
       </c>
       <c r="J8" s="10">
-        <v>2.6699051405144898</v>
+        <v>2.6699045727986999</v>
       </c>
       <c r="K8" s="10">
-        <v>-2.3512755530627301</v>
+        <v>-2.3512739875570898</v>
       </c>
       <c r="L8" s="10">
-        <v>1.72543166610191</v>
+        <v>1.72543080745</v>
       </c>
       <c r="M8" s="10">
-        <v>6.0472233049656099</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+        <v>6.0567307960024799</v>
+      </c>
+      <c r="N8" s="10">
+        <v>5.5755745093265103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="10">
-        <v>-6.5991677812331</v>
+        <v>-6.5991680587235004</v>
       </c>
       <c r="C9" s="10">
-        <v>15.0652233826162</v>
+        <v>15.0652242520447</v>
       </c>
       <c r="D9" s="10">
-        <v>-1.0805316814323001</v>
+        <v>-1.0805322016979</v>
       </c>
       <c r="E9" s="10">
-        <v>4.533168278062</v>
+        <v>4.5331682376452997</v>
       </c>
       <c r="F9" s="10">
-        <v>3.6633827972266002</v>
+        <v>3.6633826385449</v>
       </c>
       <c r="G9" s="10">
-        <v>-1.9058967402061999</v>
+        <v>-1.9058964651531001</v>
       </c>
       <c r="H9" s="10">
-        <v>6.3240798644231999</v>
+        <v>6.3240809412968</v>
       </c>
       <c r="I9" s="10">
-        <v>5.0019949619644999</v>
+        <v>5.0019936404907002</v>
       </c>
       <c r="J9" s="10">
-        <v>0.38991132175729998</v>
+        <v>0.38991277856709999</v>
       </c>
       <c r="K9" s="10">
-        <v>-5.8558367405239</v>
+        <v>-5.8558373438959004</v>
       </c>
       <c r="L9" s="10">
-        <v>-1.2593250215745999</v>
+        <v>-1.2593265046888</v>
       </c>
       <c r="M9" s="10">
-        <v>9.9684239577427007</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+        <v>10.3945914828778</v>
+      </c>
+      <c r="N9" s="10">
+        <v>10.3588536005468</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="10">
-        <v>2.3423785458442001</v>
+        <v>2.3423760730202998</v>
       </c>
       <c r="C10" s="10">
-        <v>1.9971724583035799</v>
+        <v>1.9971694502855</v>
       </c>
       <c r="D10" s="10">
-        <v>1.31845180100379</v>
+        <v>1.3184516251367999</v>
       </c>
       <c r="E10" s="10">
-        <v>-0.11982644565565</v>
+        <v>-0.11982183296890001</v>
       </c>
       <c r="F10" s="10">
-        <v>1.3016455206363799</v>
+        <v>1.3016504447831001</v>
       </c>
       <c r="G10" s="10">
-        <v>1.53557444638892</v>
+        <v>1.5355754481613</v>
       </c>
       <c r="H10" s="10">
-        <v>4.2511462988465896</v>
+        <v>4.2511456020349998</v>
       </c>
       <c r="I10" s="10">
-        <v>6.0909778902768199</v>
+        <v>6.0909725435114996</v>
       </c>
       <c r="J10" s="10">
-        <v>4.31223729692553</v>
+        <v>4.3122353028553997</v>
       </c>
       <c r="K10" s="10">
-        <v>7.8218184623250003E-2</v>
+        <v>7.8221382650800003E-2</v>
       </c>
       <c r="L10" s="10">
-        <v>3.6718890802209598</v>
+        <v>3.6718886574581</v>
       </c>
       <c r="M10" s="10">
-        <v>3.7445639008105802</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+        <v>3.5093947657808</v>
+      </c>
+      <c r="N10" s="10">
+        <v>2.5798326546549002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B11" s="10">
-        <v>4.6958138800568001</v>
+        <v>4.6958135380697001</v>
       </c>
       <c r="C11" s="10">
-        <v>0.56791095037390005</v>
+        <v>0.56791070220210005</v>
       </c>
       <c r="D11" s="10">
-        <v>2.0386317426353999</v>
+        <v>2.0386320979703001</v>
       </c>
       <c r="E11" s="10">
-        <v>1.3938075023693</v>
+        <v>1.3938073326553999</v>
       </c>
       <c r="F11" s="10">
-        <v>0.96901891214989999</v>
+        <v>0.96901894154570001</v>
       </c>
       <c r="G11" s="10">
-        <v>2.1782668579607001</v>
+        <v>2.1782670617106001</v>
       </c>
       <c r="H11" s="10">
-        <v>3.8324155448893999</v>
+        <v>3.8324149080100001</v>
       </c>
       <c r="I11" s="10">
-        <v>3.8974679799084</v>
+        <v>3.8974685460604999</v>
       </c>
       <c r="J11" s="10">
-        <v>2.5083237194898</v>
+        <v>2.5083234400901002</v>
       </c>
       <c r="K11" s="10">
-        <v>1.5016349910583999</v>
+        <v>1.5016351535890999</v>
       </c>
       <c r="L11" s="10">
-        <v>1.4698482094037</v>
+        <v>1.469848586108</v>
       </c>
       <c r="M11" s="10">
-        <v>2.6930343925978</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.6930340312680001</v>
+      </c>
+      <c r="N11" s="10">
+        <v>5.1632034549445001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>26</v>
       </c>
@@ -1063,8 +1099,11 @@
       <c r="M12" s="10">
         <v>2.1309626289697001</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N12" s="10">
+        <v>2.650476607221</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
@@ -1104,131 +1143,143 @@
       <c r="M13" s="10">
         <v>2.9168946331418999</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N13" s="10">
+        <v>6.1563223153601001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B14" s="10">
-        <v>0.70018932306149995</v>
+        <v>0.7001891498292</v>
       </c>
       <c r="C14" s="10">
-        <v>2.1716066527928999</v>
+        <v>2.1716070500555</v>
       </c>
       <c r="D14" s="10">
-        <v>2.5414283591890001</v>
+        <v>2.5414278735895</v>
       </c>
       <c r="E14" s="10">
-        <v>1.6380131964278</v>
+        <v>1.6380133868255</v>
       </c>
       <c r="F14" s="10">
-        <v>1.2454467417781001</v>
+        <v>1.2454469421208001</v>
       </c>
       <c r="G14" s="10">
-        <v>1.6117177079642999</v>
+        <v>1.6117173998087</v>
       </c>
       <c r="H14" s="10">
-        <v>1.3576093431036</v>
+        <v>1.3576092762784</v>
       </c>
       <c r="I14" s="10">
-        <v>1.5002074020108001</v>
+        <v>1.5002074962109</v>
       </c>
       <c r="J14" s="10">
-        <v>1.0542647721153999</v>
+        <v>1.0542649537694999</v>
       </c>
       <c r="K14" s="10">
-        <v>1.2812202742276</v>
+        <v>1.2812206005125999</v>
       </c>
       <c r="L14" s="10">
-        <v>0.97900970370439999</v>
+        <v>0.9790093828591</v>
       </c>
       <c r="M14" s="10">
-        <v>2.2643713123396001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.0683092077327001</v>
+      </c>
+      <c r="N14" s="10">
+        <v>0.87864961847750001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="10">
-        <v>0.72024033799060005</v>
+        <v>0.72024013599360004</v>
       </c>
       <c r="C15" s="10">
-        <v>1.282759886115</v>
+        <v>1.2827603320425001</v>
       </c>
       <c r="D15" s="10">
-        <v>2.7966691902146001</v>
+        <v>2.7966686806552001</v>
       </c>
       <c r="E15" s="10">
-        <v>1.8135314761607999</v>
+        <v>1.8135316138432001</v>
       </c>
       <c r="F15" s="10">
-        <v>1.3285110819513</v>
+        <v>1.3285112805132999</v>
       </c>
       <c r="G15" s="10">
-        <v>1.1213884059490999</v>
+        <v>1.1213881061994</v>
       </c>
       <c r="H15" s="10">
-        <v>0.79601056339480003</v>
+        <v>0.79601050522100003</v>
       </c>
       <c r="I15" s="10">
-        <v>1.6269025147705001</v>
+        <v>1.6269026147426</v>
       </c>
       <c r="J15" s="10">
-        <v>0.79895417672129998</v>
+        <v>0.79895431867370004</v>
       </c>
       <c r="K15" s="10">
-        <v>1.1170918638688001</v>
+        <v>1.1170923341528001</v>
       </c>
       <c r="L15" s="10">
-        <v>1.0063600204975001</v>
+        <v>1.0063596351290001</v>
       </c>
       <c r="M15" s="10">
-        <v>2.1463794199052999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.9269897876719999</v>
+      </c>
+      <c r="N15" s="10">
+        <v>0.53107299599750002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="10">
-        <v>-0.77240200945469994</v>
+        <v>-0.77240198556328998</v>
       </c>
       <c r="C16" s="10">
-        <v>-0.50832742969779998</v>
+        <v>-0.50832748211690004</v>
       </c>
       <c r="D16" s="10">
-        <v>2.0201306789319</v>
+        <v>2.0201308905379398</v>
       </c>
       <c r="E16" s="10">
-        <v>0.29004101515149999</v>
+        <v>0.29004079197376997</v>
       </c>
       <c r="F16" s="10">
-        <v>1.1607883475633001</v>
+        <v>1.1607885684935999</v>
       </c>
       <c r="G16" s="10">
-        <v>-1.1221467797002</v>
+        <v>-1.1221473233479999</v>
       </c>
       <c r="H16" s="10">
-        <v>0.63301238763970002</v>
+        <v>0.63301231806135005</v>
       </c>
       <c r="I16" s="10">
-        <v>1.5163892460407</v>
+        <v>1.5163898549906101</v>
       </c>
       <c r="J16" s="10">
-        <v>0.73018370756039996</v>
+        <v>0.73018401947961997</v>
       </c>
       <c r="K16" s="10">
-        <v>1.563411369123</v>
+        <v>1.56341139478404</v>
       </c>
       <c r="L16" s="10">
-        <v>0.15976345010429999</v>
+        <v>0.15976314718755</v>
       </c>
       <c r="M16" s="10">
-        <v>0.79194589155649997</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+        <v>3.5817739664450003E-2</v>
+      </c>
+      <c r="N16" s="10">
+        <v>0.15056045487950001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="24" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>28</v>
       </c>
@@ -1268,8 +1319,11 @@
       <c r="M17" s="10">
         <v>2.9095941615158001</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N17" s="10">
+        <v>1.0416202971952</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>29</v>
       </c>
@@ -1309,8 +1363,11 @@
       <c r="M18" s="10">
         <v>2.3967106256581001</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N18" s="10">
+        <v>0.16042004310729999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>30</v>
       </c>
@@ -1350,8 +1407,11 @@
       <c r="M19" s="10">
         <v>1.5265079429830699</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N19" s="10">
+        <v>3.8634163513156898</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>31</v>
       </c>
@@ -1391,172 +1451,187 @@
       <c r="M20" s="10">
         <v>13.8702143077205</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N20" s="10">
+        <v>3.2093257537598001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
       <c r="B21" s="10">
-        <v>3.0186596763060001</v>
+        <v>3.018659398679</v>
       </c>
       <c r="C21" s="10">
-        <v>2.6725479792610001</v>
+        <v>2.6725484714399999</v>
       </c>
       <c r="D21" s="10">
-        <v>2.8910951509260001</v>
+        <v>2.8910957024520001</v>
       </c>
       <c r="E21" s="10">
-        <v>2.5341836420020001</v>
+        <v>2.534184086747</v>
       </c>
       <c r="F21" s="10">
-        <v>3.030647393837</v>
+        <v>3.0306475886180002</v>
       </c>
       <c r="G21" s="10">
-        <v>3.199108896607</v>
+        <v>3.1991088760149999</v>
       </c>
       <c r="H21" s="10">
-        <v>2.6441239121179998</v>
+        <v>2.64412332188</v>
       </c>
       <c r="I21" s="10">
-        <v>2.7675779752710001</v>
+        <v>2.767577788498</v>
       </c>
       <c r="J21" s="10">
-        <v>2.83581873296</v>
+        <v>2.835818529475</v>
       </c>
       <c r="K21" s="10">
-        <v>2.8539696138839998</v>
+        <v>2.8539698957190001</v>
       </c>
       <c r="L21" s="10">
-        <v>2.889544166141</v>
+        <v>2.8895442807879999</v>
       </c>
       <c r="M21" s="10">
-        <v>2.6697211680209998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.3603582298500001</v>
+      </c>
+      <c r="N21" s="10">
+        <v>2.6922093799160001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="10">
-        <v>5.1143205273110004</v>
+        <v>5.1143194867500004</v>
       </c>
       <c r="C22" s="10">
-        <v>4.273880585793</v>
+        <v>4.2738827783659996</v>
       </c>
       <c r="D22" s="10">
-        <v>4.4333845316230001</v>
+        <v>4.4333861455939996</v>
       </c>
       <c r="E22" s="10">
-        <v>4.1065377220729999</v>
+        <v>4.1065395678719998</v>
       </c>
       <c r="F22" s="10">
-        <v>4.362635992964</v>
+        <v>4.3626364472779997</v>
       </c>
       <c r="G22" s="10">
-        <v>3.9470763827909998</v>
+        <v>3.947076088557</v>
       </c>
       <c r="H22" s="10">
-        <v>3.617673787522</v>
+        <v>3.617671821828</v>
       </c>
       <c r="I22" s="10">
-        <v>3.1438412573279999</v>
+        <v>3.143840638695</v>
       </c>
       <c r="J22" s="10">
-        <v>3.4097346860190001</v>
+        <v>3.409734123882</v>
       </c>
       <c r="K22" s="10">
-        <v>3.3851847608179999</v>
+        <v>3.3851854689979999</v>
       </c>
       <c r="L22" s="10">
-        <v>3.1814749764650001</v>
+        <v>3.1814757357789998</v>
       </c>
       <c r="M22" s="10">
-        <v>2.7967164843629999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.9185674975999998</v>
+      </c>
+      <c r="N22" s="10">
+        <v>3.0139199790059998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="10">
-        <v>2.3674163189069999</v>
+        <v>2.3674161836119998</v>
       </c>
       <c r="C23" s="10">
-        <v>2.2756513042350002</v>
+        <v>2.2756514250139999</v>
       </c>
       <c r="D23" s="10">
-        <v>2.3633369553599999</v>
+        <v>2.3633374667089999</v>
       </c>
       <c r="E23" s="10">
-        <v>1.6818083498450001</v>
+        <v>1.6818080602000001</v>
       </c>
       <c r="F23" s="10">
-        <v>2.0976152685140002</v>
+        <v>2.0976149958920001</v>
       </c>
       <c r="G23" s="10">
-        <v>2.4852725031570002</v>
+        <v>2.4852726919600001</v>
       </c>
       <c r="H23" s="10">
-        <v>2.6616260191999999</v>
+        <v>2.661626089926</v>
       </c>
       <c r="I23" s="10">
-        <v>2.7392883771299998</v>
+        <v>2.73928832585</v>
       </c>
       <c r="J23" s="10">
-        <v>2.5905011465190002</v>
+        <v>2.590501183982</v>
       </c>
       <c r="K23" s="10">
-        <v>2.5757062716919998</v>
+        <v>2.5757065965349999</v>
       </c>
       <c r="L23" s="10">
-        <v>2.6174412414789998</v>
+        <v>2.6174413212259999</v>
       </c>
       <c r="M23" s="10">
-        <v>2.5022404686350002</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.2546495508889999</v>
+      </c>
+      <c r="N23" s="10">
+        <v>2.170995796897</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B24" s="10">
-        <v>4.2034500970759998</v>
+        <v>4.2034504319900998</v>
       </c>
       <c r="C24" s="10">
-        <v>3.027147412258</v>
+        <v>3.0271471982743998</v>
       </c>
       <c r="D24" s="10">
-        <v>2.801571139849</v>
+        <v>2.8015709806753999</v>
       </c>
       <c r="E24" s="10">
-        <v>3.3905754786850002</v>
+        <v>3.3905757556031002</v>
       </c>
       <c r="F24" s="10">
-        <v>3.1576092816729999</v>
+        <v>3.1576089280109998</v>
       </c>
       <c r="G24" s="10">
-        <v>2.47456751627</v>
+        <v>2.4745678293645001</v>
       </c>
       <c r="H24" s="10">
-        <v>1.9526162507639999</v>
+        <v>1.9526164118302001</v>
       </c>
       <c r="I24" s="10">
-        <v>3.023568110472</v>
+        <v>3.0235681098513001</v>
       </c>
       <c r="J24" s="10">
-        <v>3.9434195688889999</v>
+        <v>3.9434196469603999</v>
       </c>
       <c r="K24" s="10">
-        <v>3.2481757798099999</v>
+        <v>3.2481754837996002</v>
       </c>
       <c r="L24" s="10">
-        <v>3.016984466732</v>
+        <v>3.0169845119302998</v>
       </c>
       <c r="M24" s="10">
-        <v>3.0750396608770001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+        <v>-0.11200071823670001</v>
+      </c>
+      <c r="N24" s="10">
+        <v>1.2139927027455999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>32</v>
       </c>
@@ -1596,49 +1671,55 @@
       <c r="M25" s="10">
         <v>5.3457242875939999</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N25" s="10">
+        <v>8.7274872697273995</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B26" s="11">
-        <v>1.713789578099</v>
+        <v>1.7137895871169999</v>
       </c>
       <c r="C26" s="11">
-        <v>2.310555771477</v>
+        <v>2.3105557901560001</v>
       </c>
       <c r="D26" s="11">
-        <v>2.8501023847429998</v>
+        <v>2.8501026121909998</v>
       </c>
       <c r="E26" s="11">
-        <v>2.465958088971</v>
+        <v>2.4659581377839999</v>
       </c>
       <c r="F26" s="11">
-        <v>3.1096213069630001</v>
+        <v>3.1096218759130001</v>
       </c>
       <c r="G26" s="11">
-        <v>2.88175510635</v>
+        <v>2.8817550422320002</v>
       </c>
       <c r="H26" s="11">
-        <v>2.344785182256</v>
+        <v>2.3447847654179999</v>
       </c>
       <c r="I26" s="11">
-        <v>2.8735885518259998</v>
+        <v>2.8735885562760002</v>
       </c>
       <c r="J26" s="11">
-        <v>2.7567870894230002</v>
+        <v>2.7567868693539999</v>
       </c>
       <c r="K26" s="11">
-        <v>2.8453434083409999</v>
+        <v>2.8453434688580002</v>
       </c>
       <c r="L26" s="11">
-        <v>2.6909648523879999</v>
+        <v>2.6909647044099998</v>
       </c>
       <c r="M26" s="11">
-        <v>2.2447938728970001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2.9946598322379998</v>
+      </c>
+      <c r="N26" s="11">
+        <v>2.9427920453660001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
